--- a/tests/Fixtures/Inventory/SYNTHETIC_inventory_valid.xlsx
+++ b/tests/Fixtures/Inventory/SYNTHETIC_inventory_valid.xlsx
@@ -23,7 +23,7 @@
     <definedName name="OperatingModels">Lists!$A$2:$A$3</definedName>
     <definedName name="PropertyStatuses">Lists!$B$2:$B$6</definedName>
     <definedName name="SpaceTypes">Lists!$C$2:$C$7</definedName>
-    <definedName name="InventoryModes">Lists!$D$2:$D$4</definedName>
+    <definedName name="InventoryModes">Lists!$D$2:$D$5</definedName>
     <definedName name="SpaceStatuses">Lists!$E$2:$E$5</definedName>
     <definedName name="YesNo">Lists!$F$2:$F$3</definedName>
     <definedName name="Weekdays">Lists!$G$2:$G$8</definedName>
@@ -556,7 +556,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Template SG-INV-1.1 · draft generated 2026-10-24 · status: DRAFT pending owner questions Q-OW-1 (floor allocation), Q-OW-2 (property grouping), Q-OW-7 (hybrid zones)</t>
+          <t>Template SG-INV-1.2 · draft generated 2026-10-24 · status: DRAFT; floors per property still to be supplied (Q-OW-1). Each address is its own property; current properties are owned and operated.</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="10">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1. Fill the sheets in order: Property → Buildings → Hours → Floors → Spaces → Seats (only 'Per seat' spaces) → Occupancy → Amenities.</t>
+          <t>1. Fill the sheets in order: Property → Buildings → Hours → Floors → Spaces → Seats ('Per seat' and 'Hybrid' spaces) → Occupancy → Amenities.</t>
         </is>
       </c>
     </row>
@@ -647,14 +647,14 @@
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Space type → allowed inventory modes (proposed defaults, ADR-0013): Private cabin, Meeting room, Conference / training room, Office suite → Whole space · Dedicated desk zone → Per seat · Flexible seating zone → Pooled or Per seat.</t>
+          <t>Space type → allowed inventory modes (proposed defaults, ADR-0013): Private cabin, Meeting room, Conference / training room, Office suite → Whole space · Dedicated desk zone → Per seat or Hybrid · Flexible seating zone → Pooled, Per seat or Hybrid.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Product category → required inventory mode: Private cabins / private offices, Meeting rooms, Conference and training rooms, Managed offices for enterprises → Whole space · Dedicated desks → Per seat · Hot desks / flexible seating → Pooled or Per seat · Virtual office / business address → not a physical space (never listed under sellable_as).</t>
+          <t>Product category → required inventory mode: Private cabins / private offices, Meeting rooms, Conference and training rooms, Managed offices for enterprises → Whole space · Dedicated desks → Per seat or Hybrid · Hot desks / flexible seating → Pooled, Per seat or Hybrid · Virtual office / business address → not a physical space (never listed under sellable_as).</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Seats: Individual seats, only for spaces with inventory mode 'Per seat'.</t>
+          <t>Seats: Individual seats, only for spaces with inventory mode 'Per seat' or 'Hybrid (seats + pool)'.</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1005,11 @@
           <t>Meeting room</t>
         </is>
       </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid (seats + pool)</t>
+        </is>
+      </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Decommissioned</t>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>SG-INV-1.1</t>
+          <t>SG-INV-1.2</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1247,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Required. City name as it should appear publicly (see owner question Q-OW-4).</t>
+          <t>Required. Official current city name, e.g. Noida, Gurugram, Delhi, Faridabad, Ghaziabad.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -10286,7 +10291,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -10419,7 +10424,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Required. Whole space = one occupant; Per seat = each seat tracked; Pooled = shared capacity.</t>
+          <t>Required. Whole space = one occupant; Per seat = each seat tracked; Pooled = shared capacity; Hybrid = some seats assigned, the rest shared.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -11371,12 +11376,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA</t>
+          <t>SYN-ALPHA</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA-A</t>
+          <t>SYN-ALPHA-B</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
@@ -11384,29 +11389,29 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA-01-PC-01</t>
+          <t>SYN-ALPHA-B1-HY-01</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Cabin 1.01</t>
+          <t>Hybrid desks B1</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Private cabin</t>
+          <t>Flexible seating zone</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Whole space</t>
+          <t>Hybrid (seats + pool)</t>
         </is>
       </c>
       <c r="H16" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>420</v>
+        <v>700</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
@@ -11415,12 +11420,12 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Private cabins / private offices</t>
+          <t>Dedicated desks; Hot desks / flexible seating</t>
         </is>
       </c>
       <c r="M16" s="12" t="n"/>
@@ -11449,17 +11454,17 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA-01-MR-01</t>
+          <t>SYN-BETA-01-PC-01</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Meeting room Pine</t>
+          <t>Cabin 1.01</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Meeting room</t>
+          <t>Private cabin</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -11471,61 +11476,107 @@
         <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>Private cabins / private offices</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="inlineStr">
+        <is>
+          <t>SYNTHETIC test data</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>SYN-BETA</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>SYN-BETA-A</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>SYN-BETA-01-MR-01</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Meeting room Pine</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Meeting room</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Whole space</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>Meeting rooms</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr">
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>Video conferencing screen; Whiteboard</t>
         </is>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="O17" s="12" t="n">
+      <c r="O18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="P18" s="12" t="n">
         <v>480</v>
       </c>
-      <c r="Q17" s="12" t="inlineStr">
+      <c r="Q18" s="12" t="inlineStr">
         <is>
           <t>SYNTHETIC test data</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -15119,7 +15170,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Required. Per-seat space code from the Spaces sheet.</t>
+          <t>Required. Per-seat or hybrid space code from the Spaces sheet.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -15355,54 +15406,174 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="12" t="n"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="12" t="n"/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="12" t="n"/>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="12" t="n"/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="12" t="n"/>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>H-05</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="12" t="n"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>H-06</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="12" t="n"/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>H-07</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="12" t="n"/>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>H-08</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="12" t="n"/>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>H-09</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="12" t="n"/>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>H-10</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -16373,7 +16544,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Optional. Per-seat spaces only: the seat allocated.</t>
+          <t>Optional. Per-seat or hybrid spaces: the seat assigned. Leave blank for pooled seats in a hybrid zone.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -16642,34 +16813,96 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>SYN-AGR-0007</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>46538</v>
+      </c>
       <c r="G11" s="13" t="n"/>
-      <c r="H11" s="12" t="n"/>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>SYN-AGR-0007</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>46538</v>
+      </c>
       <c r="G12" s="13" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
       <c r="B13" s="11" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>SYN-AGR-0008</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>46568</v>
+      </c>
       <c r="G13" s="13" t="n"/>
-      <c r="H13" s="12" t="n"/>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>

--- a/tests/Fixtures/Inventory/SYNTHETIC_inventory_valid.xlsx
+++ b/tests/Fixtures/Inventory/SYNTHETIC_inventory_valid.xlsx
@@ -556,7 +556,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Template SG-INV-1.2 · draft generated 2026-10-24 · status: DRAFT; floors per property still to be supplied (Q-OW-1). Each address is its own property; current properties are owned and operated.</t>
+          <t>Template SG-INV-1.3 · draft generated 2026-10-24 · status: DRAFT; floors per property still to be supplied (Q-OW-1). Each address is its own property; current properties are owned and operated.</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>SG-INV-1.2</t>
+          <t>SG-INV-1.3</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>centre_manager_email</t>
+          <t>property_manager_email</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Optional. Work email of the SmartGro centre manager (staff only).</t>
+          <t>Optional. Work email of the SmartGro Property Manager (staff only).</t>
         </is>
       </c>
     </row>
